--- a/NanaSalesDash (2).xlsx
+++ b/NanaSalesDash (2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user_1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5310CEF2-E930-4A77-AA81-5EA174123582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E863B4-A531-40C2-8291-9B6010972457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{8EF8AC24-7DE8-4383-99F5-3A777DAE6CFC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="4" xr2:uid="{8EF8AC24-7DE8-4383-99F5-3A777DAE6CFC}"/>
   </bookViews>
   <sheets>
     <sheet name="PriceTable" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,8 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="16" r:id="rId8"/>
-    <pivotCache cacheId="11" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="169">
   <si>
     <t>Product</t>
   </si>
@@ -351,6 +351,213 @@
   <si>
     <t>Amount</t>
   </si>
+  <si>
+    <t>Luku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abel </t>
+  </si>
+  <si>
+    <t>Packaging</t>
+  </si>
+  <si>
+    <t>Dawa</t>
+  </si>
+  <si>
+    <t>Olive Oil &amp; Nana</t>
+  </si>
+  <si>
+    <t>Moper Set</t>
+  </si>
+  <si>
+    <t>Liquid Soap</t>
+  </si>
+  <si>
+    <t>Lunch</t>
+  </si>
+  <si>
+    <t>Tithe</t>
+  </si>
+  <si>
+    <t>Nana</t>
+  </si>
+  <si>
+    <t>Toilet Brush</t>
+  </si>
+  <si>
+    <t>Mahindi Mabichi</t>
+  </si>
+  <si>
+    <t>Nancy CRDB</t>
+  </si>
+  <si>
+    <t>Butter Bim</t>
+  </si>
+  <si>
+    <t>Caustic &amp; Transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fragrance Oils </t>
+  </si>
+  <si>
+    <t>Maji</t>
+  </si>
+  <si>
+    <t>Tumetuma Salim Ally</t>
+  </si>
+  <si>
+    <t>Vigo Pazia</t>
+  </si>
+  <si>
+    <t>Abel Bim</t>
+  </si>
+  <si>
+    <t>Sticker</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Nancy Sadaka</t>
+  </si>
+  <si>
+    <t>Nancy Unga</t>
+  </si>
+  <si>
+    <t>Abel</t>
+  </si>
+  <si>
+    <t>Abel (maji&amp; lulu &amp; package)</t>
+  </si>
+  <si>
+    <t>Abel Sokon</t>
+  </si>
+  <si>
+    <t>Lunch Nancy</t>
+  </si>
+  <si>
+    <t>Abel (Carpet)</t>
+  </si>
+  <si>
+    <t>Ulinzi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taka </t>
+  </si>
+  <si>
+    <t>Moja Tax</t>
+  </si>
+  <si>
+    <t>Mkate</t>
+  </si>
+  <si>
+    <t>Fundi Nguo</t>
+  </si>
+  <si>
+    <t>Abel Moshi</t>
+  </si>
+  <si>
+    <t>Nancy Lunch</t>
+  </si>
+  <si>
+    <t>Mzigo</t>
+  </si>
+  <si>
+    <t>Abel Mzigo Dar</t>
+  </si>
+  <si>
+    <t>Nana Lipa No</t>
+  </si>
+  <si>
+    <t>Umeme</t>
+  </si>
+  <si>
+    <t>Viungo</t>
+  </si>
+  <si>
+    <t>Mahindi</t>
+  </si>
+  <si>
+    <t>Marry</t>
+  </si>
+  <si>
+    <t>Scones</t>
+  </si>
+  <si>
+    <t>Maji &amp; 3000</t>
+  </si>
+  <si>
+    <t>Boda</t>
+  </si>
+  <si>
+    <t>Mafuta</t>
+  </si>
+  <si>
+    <t>Nancy Salio</t>
+  </si>
+  <si>
+    <t>Nancy Nauli</t>
+  </si>
+  <si>
+    <t>Abel Mzigo Iringa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sukari </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundi </t>
+  </si>
+  <si>
+    <t>Nancy (lulu)</t>
+  </si>
+  <si>
+    <t>Control Number</t>
+  </si>
+  <si>
+    <t>Fundi saa</t>
+  </si>
+  <si>
+    <t>Tumetuma Mussa</t>
+  </si>
+  <si>
+    <t>Bim</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Francis</t>
+  </si>
+  <si>
+    <t>Lunch Nancy &amp; Lulu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch </t>
+  </si>
+  <si>
+    <t>Soap Oils</t>
+  </si>
+  <si>
+    <t>Wipes (Nana)</t>
+  </si>
+  <si>
+    <t>Nancy Dawa</t>
+  </si>
+  <si>
+    <t>Nancy (NMB)</t>
+  </si>
+  <si>
+    <t>Fundi Viatu</t>
+  </si>
+  <si>
+    <t>Mafuta Ya Sabuni</t>
+  </si>
+  <si>
+    <t>TRA</t>
+  </si>
+  <si>
+    <t>AUWSA</t>
+  </si>
 </sst>
 </file>
 
@@ -500,7 +707,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -534,24 +741,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$TZS]\ * #,##0_);_([$TZS]\ * \(#,##0\);_([$TZS]\ * &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$TZS]\ * #,##0_);_([$TZS]\ * \(#,##0\);_([$TZS]\ * &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$TZS]\ * #,##0_);_([$TZS]\ * \(#,##0\);_([$TZS]\ * &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_([$TZS]\ * #,##0_);_([$TZS]\ * \(#,##0\);_([$TZS]\ * &quot;-&quot;_);_(@_)"/>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <numFmt numFmtId="164" formatCode="_([$TZS]\ * #,##0_);_([$TZS]\ * \(#,##0\);_([$TZS]\ * &quot;-&quot;_);_(@_)"/>
     </dxf>
@@ -21988,7 +22184,287 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF8E7D47-1F2D-443A-8C9A-EA491B714E8C}" name="PivotTable13" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34D8DF47-FBA9-4FDC-8837-3DCBDB1EEFF8}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+  <location ref="L3:M9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="31">
+        <item x="7"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="11"/>
+        <item x="17"/>
+        <item x="2"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="21"/>
+        <item x="10"/>
+        <item x="15"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="6"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="1" numFmtId="166"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="3" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B54F011F-D417-4CAB-88F2-D7ED9C72C463}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A57:B63" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="47">
+        <item x="18"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item x="33"/>
+        <item x="16"/>
+        <item x="31"/>
+        <item x="41"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="17"/>
+        <item x="21"/>
+        <item x="32"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="1"/>
+        <item x="36"/>
+        <item x="26"/>
+        <item x="29"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item m="1" x="45"/>
+        <item x="39"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="30"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="40"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units Sold" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="2" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF8E7D47-1F2D-443A-8C9A-EA491B714E8C}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="D81:E98" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0" measureFilter="1">
@@ -22141,149 +22617,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3EDE172-D96E-4595-94FF-099A4802F98A}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="L24:M30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="31">
-        <item x="7"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="11"/>
-        <item x="17"/>
-        <item x="2"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="21"/>
-        <item x="10"/>
-        <item x="15"/>
-        <item x="19"/>
-        <item x="14"/>
-        <item x="18"/>
-        <item x="12"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="6"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="29"/>
-        <item x="28"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="7" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 top="0" val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8AF861F5-5538-436C-9688-5D3F365900CD}" name="PivotTable10" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8AF861F5-5538-436C-9688-5D3F365900CD}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="L74:M82" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
@@ -22454,8 +22789,89 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39548950-D4FC-4B51-9985-0CD974F93498}" name="PivotTable9" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{800D7462-6A29-4825-986B-A4D6B4A6DF0C}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A49:B53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39548950-D4FC-4B51-9985-0CD974F93498}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
   <location ref="L57:M64" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
@@ -22614,509 +23030,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C1895EB-5D13-4233-B748-E3D57F229A90}" name="PivotTable7" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
-  <location ref="A90:B94" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0">
-      <items count="47">
-        <item x="38"/>
-        <item x="25"/>
-        <item x="18"/>
-        <item x="36"/>
-        <item x="24"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="8"/>
-        <item x="33"/>
-        <item x="16"/>
-        <item x="31"/>
-        <item x="35"/>
-        <item x="41"/>
-        <item x="6"/>
-        <item x="42"/>
-        <item x="28"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="11"/>
-        <item x="15"/>
-        <item x="17"/>
-        <item x="27"/>
-        <item x="21"/>
-        <item x="20"/>
-        <item x="19"/>
-        <item x="32"/>
-        <item x="7"/>
-        <item x="10"/>
-        <item x="40"/>
-        <item x="30"/>
-        <item x="14"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="39"/>
-        <item x="12"/>
-        <item x="43"/>
-        <item x="23"/>
-        <item x="29"/>
-        <item x="26"/>
-        <item m="1" x="45"/>
-        <item x="0"/>
-        <item x="34"/>
-        <item x="1"/>
-        <item x="44"/>
-        <item x="37"/>
-        <item x="22"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="4">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="3">
-    <chartFormat chart="3" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B54F011F-D417-4CAB-88F2-D7ED9C72C463}" name="PivotTable6" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="A57:B63" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="47">
-        <item x="18"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="8"/>
-        <item x="33"/>
-        <item x="16"/>
-        <item x="31"/>
-        <item x="41"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="17"/>
-        <item x="21"/>
-        <item x="32"/>
-        <item x="7"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="1"/>
-        <item x="36"/>
-        <item x="26"/>
-        <item x="29"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="11"/>
-        <item m="1" x="45"/>
-        <item x="39"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="30"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="40"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Units Sold" fld="3" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="2" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34D8DF47-FBA9-4FDC-8837-3DCBDB1EEFF8}" name="PivotTable3" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="L3:M9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="31">
-        <item x="7"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="11"/>
-        <item x="17"/>
-        <item x="2"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="21"/>
-        <item x="10"/>
-        <item x="15"/>
-        <item x="19"/>
-        <item x="14"/>
-        <item x="18"/>
-        <item x="12"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="6"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="29"/>
-        <item x="28"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="1" numFmtId="166"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="3" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{800D7462-6A29-4825-986B-A4D6B4A6DF0C}" name="PivotTable5" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="A49:B53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="5">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="3" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D18FBB9-AD90-41FB-B086-B9827B3791C9}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D18FBB9-AD90-41FB-B086-B9827B3791C9}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A32:B39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
@@ -23241,8 +23156,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E010326A-350C-4073-AE02-22874A8C31CE}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E010326A-350C-4073-AE02-22874A8C31CE}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A2:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
@@ -23364,6 +23279,287 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C1895EB-5D13-4233-B748-E3D57F229A90}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+  <location ref="A90:B94" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0">
+      <items count="47">
+        <item x="38"/>
+        <item x="25"/>
+        <item x="18"/>
+        <item x="36"/>
+        <item x="24"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item x="33"/>
+        <item x="16"/>
+        <item x="31"/>
+        <item x="35"/>
+        <item x="41"/>
+        <item x="6"/>
+        <item x="42"/>
+        <item x="28"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item x="15"/>
+        <item x="17"/>
+        <item x="27"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="32"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="40"/>
+        <item x="30"/>
+        <item x="14"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="39"/>
+        <item x="12"/>
+        <item x="43"/>
+        <item x="23"/>
+        <item x="29"/>
+        <item x="26"/>
+        <item m="1" x="45"/>
+        <item x="0"/>
+        <item x="34"/>
+        <item x="1"/>
+        <item x="44"/>
+        <item x="37"/>
+        <item x="22"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3EDE172-D96E-4595-94FF-099A4802F98A}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="L24:M30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="31">
+        <item x="7"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="11"/>
+        <item x="17"/>
+        <item x="2"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="21"/>
+        <item x="10"/>
+        <item x="15"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="6"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="7" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 top="0" val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Month" xr10:uid="{4C239787-9D8A-45A1-94E6-FF24E9849556}" sourceName="Month">
   <data>
@@ -23389,10 +23585,10 @@
   <autoFilter ref="A1:F234" xr:uid="{32A31FE1-28CE-462B-A38B-F47C4102ADB4}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{0F5F4B0E-DE41-4AC4-A5DD-1FED5AA92CF2}" name="Product"/>
-    <tableColumn id="2" xr3:uid="{01F667A7-B028-4786-818F-1FD3CA73A9B9}" name="Date" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{5CD0FB50-DBFD-4A9B-8D2C-E9C820EB9E8F}" name="Month" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{01F667A7-B028-4786-818F-1FD3CA73A9B9}" name="Date" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{5CD0FB50-DBFD-4A9B-8D2C-E9C820EB9E8F}" name="Month" dataDxfId="3"/>
     <tableColumn id="4" xr3:uid="{F44A269E-29F1-41ED-950D-E328D0B184F5}" name="Units Sold"/>
-    <tableColumn id="5" xr3:uid="{859EE7B9-1C54-4EB5-AEC9-52FD370826E5}" name="Revenue" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{859EE7B9-1C54-4EB5-AEC9-52FD370826E5}" name="Revenue" dataDxfId="2"/>
     <tableColumn id="6" xr3:uid="{C86B5E4D-3796-4BA7-937E-CF99F0AE8742}" name="Column1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -28540,7 +28736,7 @@
         <v>46024</v>
       </c>
       <c r="C4" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(B4, "mmm")</f>
         <v>Jan</v>
       </c>
       <c r="D4">
@@ -34103,7 +34299,7 @@
         <v>46106</v>
       </c>
       <c r="C297" t="str">
-        <f t="shared" ref="C297:C328" si="4">TEXT(B297, "mmm")</f>
+        <f t="shared" ref="C297:C323" si="4">TEXT(B297, "mmm")</f>
         <v>Mar</v>
       </c>
       <c r="D297">
@@ -35300,13 +35496,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CF5A907-9500-42F7-95E7-825FAB1558A1}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="53.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -35319,12 +35519,2138 @@
       <c r="D1" t="s">
         <v>98</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="13" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>46027</v>
+      </c>
+      <c r="B2" t="str">
+        <f>TEXT(A2, "mmm")</f>
+        <v>Jan</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="str">
+        <f>IF(ISNUMBER(SEARCH("nauli",LOWER(C2))),"Logistics",
+IF(ISNUMBER(SEARCH("lunch",LOWER(C2))),"Misc",
+IF(OR(ISNUMBER(SEARCH("luku",LOWER(C2))),ISNUMBER(SEARCH("umeme",LOWER(C2)))),"Operating",
+IF(ISNUMBER(SEARCH("boda",LOWER(C2))),"Logistics",
+IF(ISNUMBER(SEARCH("abel",LOWER(C2))),"Logistics",
+IF(ISNUMBER(SEARCH("toyo",LOWER(C2))),"Logistics",
+IF(ISNUMBER(SEARCH("mary",LOWER(C2))),"Salaries",
+IF(ISNUMBER(SEARCH("soap",LOWER(C2))),"Production",
+IF(ISNUMBER(SEARCH("fragrance",LOWER(C2))),"Production",
+IF(ISNUMBER(SEARCH("gohil",LOWER(C2))),"Production",
+IF(ISNUMBER(SEARCH("formulator",LOWER(C2))),"Production",
+IF(ISNUMBER(SEARCH("shea",LOWER(C2))),"Production",
+IF(ISNUMBER(SEARCH("olive",LOWER(C2))),"Production",
+IF(ISNUMBER(SEARCH("pack",LOWER(C2))),"Production",
+IF(ISNUMBER(SEARCH("sticker",LOWER(C2))),"Production",
+IF(ISNUMBER(SEARCH("ulinzi",LOWER(C2))),"Operating",
+IF(ISNUMBER(SEARCH("taka",LOWER(C2))),"Operating",
+IF(C2="TRA","Taxes",
+IF(C2="AUWSA","Operating",
+"Misc")))))))))))))))))))</f>
+        <v>Operating</v>
+      </c>
+      <c r="E2" s="13">
+        <v>20000</v>
+      </c>
+      <c r="G2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="13">
+        <f>SUM(E2:E41)</f>
+        <v>548300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>46029</v>
+      </c>
+      <c r="B3" t="str">
+        <f t="shared" ref="B3:B66" si="0">TEXT(A3, "mmm")</f>
+        <v>Jan</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D66" si="1">IF(ISNUMBER(SEARCH("nauli",LOWER(C3))),"Logistics",
+IF(ISNUMBER(SEARCH("lunch",LOWER(C3))),"Misc",
+IF(OR(ISNUMBER(SEARCH("luku",LOWER(C3))),ISNUMBER(SEARCH("umeme",LOWER(C3)))),"Operating",
+IF(ISNUMBER(SEARCH("boda",LOWER(C3))),"Logistics",
+IF(ISNUMBER(SEARCH("abel",LOWER(C3))),"Logistics",
+IF(ISNUMBER(SEARCH("toyo",LOWER(C3))),"Logistics",
+IF(ISNUMBER(SEARCH("mary",LOWER(C3))),"Salaries",
+IF(ISNUMBER(SEARCH("soap",LOWER(C3))),"Production",
+IF(ISNUMBER(SEARCH("fragrance",LOWER(C3))),"Production",
+IF(ISNUMBER(SEARCH("gohil",LOWER(C3))),"Production",
+IF(ISNUMBER(SEARCH("formulator",LOWER(C3))),"Production",
+IF(ISNUMBER(SEARCH("shea",LOWER(C3))),"Production",
+IF(ISNUMBER(SEARCH("olive",LOWER(C3))),"Production",
+IF(ISNUMBER(SEARCH("pack",LOWER(C3))),"Production",
+IF(ISNUMBER(SEARCH("sticker",LOWER(C3))),"Production",
+IF(ISNUMBER(SEARCH("ulinzi",LOWER(C3))),"Operating",
+IF(ISNUMBER(SEARCH("taka",LOWER(C3))),"Operating",
+IF(C3="TRA","Taxes",
+IF(C3="AUWSA","Operating",
+"Misc")))))))))))))))))))</f>
+        <v>Logistics</v>
+      </c>
+      <c r="E3" s="13">
+        <v>9000</v>
+      </c>
+      <c r="G3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="13">
+        <f>SUM(E42:E89)</f>
+        <v>833000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>46034</v>
+      </c>
+      <c r="B4" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" si="1"/>
+        <v>Production</v>
+      </c>
+      <c r="E4" s="13">
+        <v>40000</v>
+      </c>
+      <c r="G4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>46034</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="1"/>
+        <v>Production</v>
+      </c>
+      <c r="E5" s="13">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>46034</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E6" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>46034</v>
+      </c>
+      <c r="B7" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="1"/>
+        <v>Production</v>
+      </c>
+      <c r="E7" s="13">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>46035</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="1"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E8" s="13">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>46035</v>
+      </c>
+      <c r="B9" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E9" s="13">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>46035</v>
+      </c>
+      <c r="B10" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="1"/>
+        <v>Production</v>
+      </c>
+      <c r="E10" s="13">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>46035</v>
+      </c>
+      <c r="B11" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E11" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>46035</v>
+      </c>
+      <c r="B12" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E12" s="13">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>46035</v>
+      </c>
+      <c r="B13" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E13" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>46036</v>
+      </c>
+      <c r="B14" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E14" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>46036</v>
+      </c>
+      <c r="B15" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E15" s="13">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>46037</v>
+      </c>
+      <c r="B16" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E16" s="13">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>46039</v>
+      </c>
+      <c r="B17" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E17" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>46039</v>
+      </c>
+      <c r="B18" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E18" s="13">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>46042</v>
+      </c>
+      <c r="B19" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="1"/>
+        <v>Production</v>
+      </c>
+      <c r="E19" s="13">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>46042</v>
+      </c>
+      <c r="B20" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E20" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>46042</v>
+      </c>
+      <c r="B21" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E21" s="13">
+        <v>21800</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>46042</v>
+      </c>
+      <c r="B22" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E22" s="13">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>46042</v>
+      </c>
+      <c r="B23" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C23" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="1"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E23" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>46043</v>
+      </c>
+      <c r="B24" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="1"/>
+        <v>Production</v>
+      </c>
+      <c r="E24" s="13">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>46043</v>
+      </c>
+      <c r="B25" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E25" s="13">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B26" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E26" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B27" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E27" s="13">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>46044</v>
+      </c>
+      <c r="B28" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E28" s="13">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>46044</v>
+      </c>
+      <c r="B29" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C29" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="1"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E29" s="13">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B30" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C30" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="1"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E30" s="13">
+        <v>25500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>46048</v>
+      </c>
+      <c r="B31" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C31" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E31" s="13">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>46048</v>
+      </c>
+      <c r="B32" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E32" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>46049</v>
+      </c>
+      <c r="B33" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C33" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" t="str">
+        <f t="shared" si="1"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E33" s="13">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>46050</v>
+      </c>
+      <c r="B34" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C34" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" t="str">
+        <f t="shared" si="1"/>
+        <v>Operating</v>
+      </c>
+      <c r="E34" s="13">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>46050</v>
+      </c>
+      <c r="B35" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C35" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" t="str">
+        <f t="shared" si="1"/>
+        <v>Operating</v>
+      </c>
+      <c r="E35" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>46050</v>
+      </c>
+      <c r="B36" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C36" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E36" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>46050</v>
+      </c>
+      <c r="B37" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C37" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E37" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>46051</v>
+      </c>
+      <c r="B38" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C38" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E38" s="13">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B39" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E39" s="13">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B40" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C40" t="s">
+        <v>133</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E40" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B41" t="str">
+        <f t="shared" si="0"/>
+        <v>Jan</v>
+      </c>
+      <c r="C41" t="s">
+        <v>134</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="1"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E41" s="13">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <v>46055</v>
+      </c>
+      <c r="B42" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C42" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E42" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <v>46057</v>
+      </c>
+      <c r="B43" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C43" t="s">
+        <v>136</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E43" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <v>46057</v>
+      </c>
+      <c r="B44" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C44" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="1"/>
+        <v>Production</v>
+      </c>
+      <c r="E44" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <v>46057</v>
+      </c>
+      <c r="B45" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C45" t="s">
+        <v>137</v>
+      </c>
+      <c r="D45" t="str">
+        <f t="shared" si="1"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E45" s="13">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <v>46058</v>
+      </c>
+      <c r="B46" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C46" t="s">
+        <v>121</v>
+      </c>
+      <c r="D46" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E46" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <v>46058</v>
+      </c>
+      <c r="B47" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C47" t="s">
+        <v>138</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E47" s="13">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <v>46058</v>
+      </c>
+      <c r="B48" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C48" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E48" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <v>46062</v>
+      </c>
+      <c r="B49" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C49" t="s">
+        <v>139</v>
+      </c>
+      <c r="D49" t="str">
+        <f t="shared" si="1"/>
+        <v>Operating</v>
+      </c>
+      <c r="E49" s="13">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <v>46064</v>
+      </c>
+      <c r="B50" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C50" t="s">
+        <v>140</v>
+      </c>
+      <c r="D50" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E50" s="13">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <v>46064</v>
+      </c>
+      <c r="B51" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C51" t="s">
+        <v>141</v>
+      </c>
+      <c r="D51" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E51" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <v>46064</v>
+      </c>
+      <c r="B52" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C52" t="s">
+        <v>142</v>
+      </c>
+      <c r="D52" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E52" s="13">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <v>46065</v>
+      </c>
+      <c r="B53" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C53" t="s">
+        <v>143</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E53" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <v>46065</v>
+      </c>
+      <c r="B54" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C54" t="s">
+        <v>144</v>
+      </c>
+      <c r="D54" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E54" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <v>46065</v>
+      </c>
+      <c r="B55" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C55" t="s">
+        <v>142</v>
+      </c>
+      <c r="D55" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E55" s="13">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <v>46065</v>
+      </c>
+      <c r="B56" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C56" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E56" s="13">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <v>46066</v>
+      </c>
+      <c r="B57" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C57" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" t="str">
+        <f t="shared" si="1"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E57" s="13">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <v>46067</v>
+      </c>
+      <c r="B58" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C58" t="s">
+        <v>146</v>
+      </c>
+      <c r="D58" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E58" s="13">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <v>46067</v>
+      </c>
+      <c r="B59" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C59" t="s">
+        <v>147</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E59" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
+        <v>46067</v>
+      </c>
+      <c r="B60" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C60" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" t="str">
+        <f t="shared" si="1"/>
+        <v>Production</v>
+      </c>
+      <c r="E60" s="13">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="3">
+        <v>46068</v>
+      </c>
+      <c r="B61" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C61" t="s">
+        <v>148</v>
+      </c>
+      <c r="D61" t="str">
+        <f t="shared" si="1"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E61" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="3">
+        <v>46069</v>
+      </c>
+      <c r="B62" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C62" t="s">
+        <v>107</v>
+      </c>
+      <c r="D62" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E62" s="13">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="3">
+        <v>46069</v>
+      </c>
+      <c r="B63" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C63" t="s">
+        <v>120</v>
+      </c>
+      <c r="D63" t="str">
+        <f t="shared" si="1"/>
+        <v>Production</v>
+      </c>
+      <c r="E63" s="13">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>46069</v>
+      </c>
+      <c r="B64" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C64" t="s">
+        <v>149</v>
+      </c>
+      <c r="D64" t="str">
+        <f t="shared" si="1"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E64" s="13">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
+        <v>46070</v>
+      </c>
+      <c r="B65" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C65" t="s">
+        <v>107</v>
+      </c>
+      <c r="D65" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E65" s="13">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="3">
+        <v>46071</v>
+      </c>
+      <c r="B66" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb</v>
+      </c>
+      <c r="C66" t="s">
+        <v>121</v>
+      </c>
+      <c r="D66" t="str">
+        <f t="shared" si="1"/>
+        <v>Misc</v>
+      </c>
+      <c r="E66" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="3">
+        <v>46071</v>
+      </c>
+      <c r="B67" t="str">
+        <f t="shared" ref="B67:B110" si="2">TEXT(A67, "mmm")</f>
+        <v>Feb</v>
+      </c>
+      <c r="C67" t="s">
+        <v>148</v>
+      </c>
+      <c r="D67" t="str">
+        <f t="shared" ref="D67:D108" si="3">IF(ISNUMBER(SEARCH("nauli",LOWER(C67))),"Logistics",
+IF(ISNUMBER(SEARCH("lunch",LOWER(C67))),"Misc",
+IF(OR(ISNUMBER(SEARCH("luku",LOWER(C67))),ISNUMBER(SEARCH("umeme",LOWER(C67)))),"Operating",
+IF(ISNUMBER(SEARCH("boda",LOWER(C67))),"Logistics",
+IF(ISNUMBER(SEARCH("abel",LOWER(C67))),"Logistics",
+IF(ISNUMBER(SEARCH("toyo",LOWER(C67))),"Logistics",
+IF(ISNUMBER(SEARCH("mary",LOWER(C67))),"Salaries",
+IF(ISNUMBER(SEARCH("soap",LOWER(C67))),"Production",
+IF(ISNUMBER(SEARCH("fragrance",LOWER(C67))),"Production",
+IF(ISNUMBER(SEARCH("gohil",LOWER(C67))),"Production",
+IF(ISNUMBER(SEARCH("formulator",LOWER(C67))),"Production",
+IF(ISNUMBER(SEARCH("shea",LOWER(C67))),"Production",
+IF(ISNUMBER(SEARCH("olive",LOWER(C67))),"Production",
+IF(ISNUMBER(SEARCH("pack",LOWER(C67))),"Production",
+IF(ISNUMBER(SEARCH("sticker",LOWER(C67))),"Production",
+IF(ISNUMBER(SEARCH("ulinzi",LOWER(C67))),"Operating",
+IF(ISNUMBER(SEARCH("taka",LOWER(C67))),"Operating",
+IF(C67="TRA","Taxes",
+IF(C67="AUWSA","Operating",
+"Misc")))))))))))))))))))</f>
+        <v>Logistics</v>
+      </c>
+      <c r="E67" s="13">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="3">
+        <v>46071</v>
+      </c>
+      <c r="B68" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D68" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E68" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="3">
+        <v>46071</v>
+      </c>
+      <c r="B69" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C69" t="s">
+        <v>141</v>
+      </c>
+      <c r="D69" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E69" s="13">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="3">
+        <v>46071</v>
+      </c>
+      <c r="B70" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C70" t="s">
+        <v>124</v>
+      </c>
+      <c r="D70" t="str">
+        <f t="shared" si="3"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E70" s="13">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="3">
+        <v>46071</v>
+      </c>
+      <c r="B71" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C71" t="s">
+        <v>151</v>
+      </c>
+      <c r="D71" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E71" s="13">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="3">
+        <v>46076</v>
+      </c>
+      <c r="B72" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C72" t="s">
+        <v>152</v>
+      </c>
+      <c r="D72" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E72" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="3">
+        <v>46076</v>
+      </c>
+      <c r="B73" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C73" t="s">
+        <v>145</v>
+      </c>
+      <c r="D73" t="str">
+        <f t="shared" si="3"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E73" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="3">
+        <v>46076</v>
+      </c>
+      <c r="B74" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C74" t="s">
+        <v>142</v>
+      </c>
+      <c r="D74" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E74" s="13">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="3">
+        <v>46076</v>
+      </c>
+      <c r="B75" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C75" t="s">
+        <v>147</v>
+      </c>
+      <c r="D75" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E75" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="3">
+        <v>46077</v>
+      </c>
+      <c r="B76" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C76" t="s">
+        <v>107</v>
+      </c>
+      <c r="D76" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E76" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="3">
+        <v>46078</v>
+      </c>
+      <c r="B77" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C77" t="s">
+        <v>124</v>
+      </c>
+      <c r="D77" t="str">
+        <f t="shared" si="3"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E77" s="13">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="3">
+        <v>46079</v>
+      </c>
+      <c r="B78" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C78" t="s">
+        <v>153</v>
+      </c>
+      <c r="D78" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E78" s="13">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="3">
+        <v>46079</v>
+      </c>
+      <c r="B79" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C79" t="s">
+        <v>154</v>
+      </c>
+      <c r="D79" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E79" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="3">
+        <v>46079</v>
+      </c>
+      <c r="B80" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C80" t="s">
+        <v>155</v>
+      </c>
+      <c r="D80" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E80" s="13">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="3">
+        <v>46079</v>
+      </c>
+      <c r="B81" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C81" t="s">
+        <v>130</v>
+      </c>
+      <c r="D81" t="str">
+        <f t="shared" si="3"/>
+        <v>Operating</v>
+      </c>
+      <c r="E81" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="3">
+        <v>46079</v>
+      </c>
+      <c r="B82" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C82" t="s">
+        <v>129</v>
+      </c>
+      <c r="D82" t="str">
+        <f t="shared" si="3"/>
+        <v>Operating</v>
+      </c>
+      <c r="E82" s="13">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="3">
+        <v>46079</v>
+      </c>
+      <c r="B83" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C83" t="s">
+        <v>107</v>
+      </c>
+      <c r="D83" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E83" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B84" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C84" t="s">
+        <v>145</v>
+      </c>
+      <c r="D84" t="str">
+        <f t="shared" si="3"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E84" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B85" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C85" t="s">
+        <v>156</v>
+      </c>
+      <c r="D85" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E85" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B86" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C86" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" t="str">
+        <f t="shared" si="3"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E86" s="13">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B87" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C87" t="s">
+        <v>157</v>
+      </c>
+      <c r="D87" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E87" s="13">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B88" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C88" t="s">
+        <v>158</v>
+      </c>
+      <c r="D88" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E88" s="13">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="3">
+        <v>46081</v>
+      </c>
+      <c r="B89" t="str">
+        <f t="shared" si="2"/>
+        <v>Feb</v>
+      </c>
+      <c r="C89" t="s">
+        <v>159</v>
+      </c>
+      <c r="D89" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E89" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B90" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C90" t="s">
+        <v>107</v>
+      </c>
+      <c r="D90" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E90" s="13">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="3">
+        <v>46085</v>
+      </c>
+      <c r="B91" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C91" t="s">
+        <v>142</v>
+      </c>
+      <c r="D91" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E91" s="13">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B92" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C92" t="s">
+        <v>160</v>
+      </c>
+      <c r="D92" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E92" s="13">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B93" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C93" t="s">
+        <v>109</v>
+      </c>
+      <c r="D93" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E93" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B94" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C94" t="s">
+        <v>161</v>
+      </c>
+      <c r="D94" t="str">
+        <f t="shared" si="3"/>
+        <v>Production</v>
+      </c>
+      <c r="E94" s="13">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B95" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C95" t="s">
+        <v>162</v>
+      </c>
+      <c r="D95" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E95" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="3">
+        <v>46090</v>
+      </c>
+      <c r="B96" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C96" t="s">
+        <v>148</v>
+      </c>
+      <c r="D96" t="str">
+        <f t="shared" si="3"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E96" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="3">
+        <v>46090</v>
+      </c>
+      <c r="B97" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C97" t="s">
+        <v>163</v>
+      </c>
+      <c r="D97" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E97" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="3">
+        <v>46088</v>
+      </c>
+      <c r="B98" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C98" t="s">
+        <v>142</v>
+      </c>
+      <c r="D98" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E98" s="13">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="3">
+        <v>46088</v>
+      </c>
+      <c r="B99" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C99" t="s">
+        <v>164</v>
+      </c>
+      <c r="D99" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E99" s="13">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="3">
+        <v>46088</v>
+      </c>
+      <c r="B100" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C100" t="s">
+        <v>127</v>
+      </c>
+      <c r="D100" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E100" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B101" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C101" t="s">
+        <v>165</v>
+      </c>
+      <c r="D101" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E101" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="3">
+        <v>46091</v>
+      </c>
+      <c r="B102" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C102" t="s">
+        <v>166</v>
+      </c>
+      <c r="D102" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E102" s="13">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B103" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C103" t="s">
+        <v>107</v>
+      </c>
+      <c r="D103" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E103" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B104" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C104" t="s">
+        <v>167</v>
+      </c>
+      <c r="D104" t="str">
+        <f t="shared" si="3"/>
+        <v>Taxes</v>
+      </c>
+      <c r="E104" s="13">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B105" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C105" t="s">
+        <v>107</v>
+      </c>
+      <c r="D105" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E105" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B106" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C106" t="s">
+        <v>120</v>
+      </c>
+      <c r="D106" t="str">
+        <f t="shared" si="3"/>
+        <v>Production</v>
+      </c>
+      <c r="E106" s="13">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B107" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C107" t="s">
+        <v>168</v>
+      </c>
+      <c r="D107" t="str">
+        <f t="shared" si="3"/>
+        <v>Operating</v>
+      </c>
+      <c r="E107" s="13">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="3">
+        <v>46097</v>
+      </c>
+      <c r="B108" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+      <c r="C108" t="s">
+        <v>121</v>
+      </c>
+      <c r="D108" t="str">
+        <f t="shared" si="3"/>
+        <v>Misc</v>
+      </c>
+      <c r="E108" s="13">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="23">
+        <v>46097</v>
+      </c>
+      <c r="B109" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="23">
+        <v>46097</v>
+      </c>
+      <c r="B110" t="str">
+        <f t="shared" si="2"/>
+        <v>Mar</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/NanaSalesDash (2).xlsx
+++ b/NanaSalesDash (2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user_1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E863B4-A531-40C2-8291-9B6010972457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20751577-47FC-48F6-B617-755C0D07A863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="4" xr2:uid="{8EF8AC24-7DE8-4383-99F5-3A777DAE6CFC}"/>
+    <workbookView xWindow="32445" yWindow="1365" windowWidth="17280" windowHeight="8970" firstSheet="2" activeTab="4" xr2:uid="{8EF8AC24-7DE8-4383-99F5-3A777DAE6CFC}"/>
   </bookViews>
   <sheets>
     <sheet name="PriceTable" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="189">
   <si>
     <t>Product</t>
   </si>
@@ -557,6 +557,66 @@
   </si>
   <si>
     <t>AUWSA</t>
+  </si>
+  <si>
+    <t>Mzigo(Boda)</t>
+  </si>
+  <si>
+    <t>stick/mackerpen</t>
+  </si>
+  <si>
+    <t>Abel(Viazi+mzigo)</t>
+  </si>
+  <si>
+    <t>Uji Nancy</t>
+  </si>
+  <si>
+    <t>Tumetumia Bisawa</t>
+  </si>
+  <si>
+    <t>Coconut Oil Packaging</t>
+  </si>
+  <si>
+    <t>Nancy(Viungo)</t>
+  </si>
+  <si>
+    <t>Mzigo Bim</t>
+  </si>
+  <si>
+    <t>Nancy &amp; Jesca</t>
+  </si>
+  <si>
+    <t>Fundi</t>
+  </si>
+  <si>
+    <t>Fomrulators Hub</t>
+  </si>
+  <si>
+    <t>Mussa</t>
+  </si>
+  <si>
+    <t>Soksi (Nancy Kids)</t>
+  </si>
+  <si>
+    <t>Abel (Nairobi)</t>
+  </si>
+  <si>
+    <t>Victor (Content)</t>
+  </si>
+  <si>
+    <t>Boda (Abel)</t>
+  </si>
+  <si>
+    <t>Mandazi</t>
+  </si>
+  <si>
+    <t>Raw Materials (soap)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Rent</t>
   </si>
 </sst>
 </file>
@@ -22184,6 +22244,292 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D18FBB9-AD90-41FB-B086-B9827B3791C9}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="A32:B39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="31">
+        <item x="7"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="11"/>
+        <item x="17"/>
+        <item x="2"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="21"/>
+        <item x="10"/>
+        <item x="15"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="6"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units Sold" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="3" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 top="0" val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39548950-D4FC-4B51-9985-0CD974F93498}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+  <location ref="L57:M64" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="47">
+        <item x="18"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item x="33"/>
+        <item x="16"/>
+        <item x="31"/>
+        <item x="41"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="17"/>
+        <item x="21"/>
+        <item x="32"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="1"/>
+        <item x="36"/>
+        <item x="26"/>
+        <item x="29"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item m="1" x="45"/>
+        <item x="39"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="30"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="40"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="1" numFmtId="166"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="3" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{34D8DF47-FBA9-4FDC-8837-3DCBDB1EEFF8}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="L3:M9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
@@ -22315,155 +22661,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B54F011F-D417-4CAB-88F2-D7ED9C72C463}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="A57:B63" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="47">
-        <item x="18"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="8"/>
-        <item x="33"/>
-        <item x="16"/>
-        <item x="31"/>
-        <item x="41"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="17"/>
-        <item x="21"/>
-        <item x="32"/>
-        <item x="7"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="1"/>
-        <item x="36"/>
-        <item x="26"/>
-        <item x="29"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="11"/>
-        <item m="1" x="45"/>
-        <item x="39"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="30"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="40"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Units Sold" fld="3" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="2" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF8E7D47-1F2D-443A-8C9A-EA491B714E8C}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="D81:E98" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
@@ -22617,7 +22815,130 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E010326A-350C-4073-AE02-22874A8C31CE}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A2:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="31">
+        <item x="7"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="11"/>
+        <item x="17"/>
+        <item x="2"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="21"/>
+        <item x="10"/>
+        <item x="15"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="6"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units Sold" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="2" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8AF861F5-5538-436C-9688-5D3F365900CD}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="L74:M82" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
@@ -22789,497 +23110,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{800D7462-6A29-4825-986B-A4D6B4A6DF0C}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="A49:B53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="0">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="3" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39548950-D4FC-4B51-9985-0CD974F93498}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
-  <location ref="L57:M64" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="47">
-        <item x="18"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="8"/>
-        <item x="33"/>
-        <item x="16"/>
-        <item x="31"/>
-        <item x="41"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="17"/>
-        <item x="21"/>
-        <item x="32"/>
-        <item x="7"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="1"/>
-        <item x="36"/>
-        <item x="26"/>
-        <item x="29"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="11"/>
-        <item m="1" x="45"/>
-        <item x="39"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="30"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="40"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="1" numFmtId="166"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="11" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="3" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D18FBB9-AD90-41FB-B086-B9827B3791C9}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="A32:B39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="31">
-        <item x="7"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="11"/>
-        <item x="17"/>
-        <item x="2"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="21"/>
-        <item x="10"/>
-        <item x="15"/>
-        <item x="19"/>
-        <item x="14"/>
-        <item x="18"/>
-        <item x="12"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="6"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="29"/>
-        <item x="28"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Units Sold" fld="3" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="3" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 top="0" val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E010326A-350C-4073-AE02-22874A8C31CE}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A2:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="31">
-        <item x="7"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="11"/>
-        <item x="17"/>
-        <item x="2"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="21"/>
-        <item x="10"/>
-        <item x="15"/>
-        <item x="19"/>
-        <item x="14"/>
-        <item x="18"/>
-        <item x="12"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="6"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="29"/>
-        <item x="28"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Units Sold" fld="3" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" evalOrder="-1" id="2" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C1895EB-5D13-4233-B748-E3D57F229A90}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="A90:B94" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
@@ -23370,7 +23201,7 @@
     <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="1">
+    <format dxfId="0">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
@@ -23419,7 +23250,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3EDE172-D96E-4595-94FF-099A4802F98A}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="L24:M30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
@@ -23545,6 +23376,235 @@
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <top10 top="0" val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{800D7462-6A29-4825-986B-A4D6B4A6DF0C}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A49:B53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B54F011F-D417-4CAB-88F2-D7ED9C72C463}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A57:B63" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="47">
+        <item x="18"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item x="33"/>
+        <item x="16"/>
+        <item x="31"/>
+        <item x="41"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="17"/>
+        <item x="21"/>
+        <item x="32"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="1"/>
+        <item x="36"/>
+        <item x="26"/>
+        <item x="29"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item m="1" x="45"/>
+        <item x="39"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="30"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="40"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units Sold" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="2" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="5" filterVal="5"/>
         </filterColumn>
       </autoFilter>
     </filter>
@@ -35496,14 +35556,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CF5A907-9500-42F7-95E7-825FAB1558A1}">
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="53.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.77734375" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -35535,26 +35595,12 @@
         <v>100</v>
       </c>
       <c r="D2" t="str">
-        <f>IF(ISNUMBER(SEARCH("nauli",LOWER(C2))),"Logistics",
-IF(ISNUMBER(SEARCH("lunch",LOWER(C2))),"Misc",
-IF(OR(ISNUMBER(SEARCH("luku",LOWER(C2))),ISNUMBER(SEARCH("umeme",LOWER(C2)))),"Operating",
-IF(ISNUMBER(SEARCH("boda",LOWER(C2))),"Logistics",
-IF(ISNUMBER(SEARCH("abel",LOWER(C2))),"Logistics",
-IF(ISNUMBER(SEARCH("toyo",LOWER(C2))),"Logistics",
-IF(ISNUMBER(SEARCH("mary",LOWER(C2))),"Salaries",
-IF(ISNUMBER(SEARCH("soap",LOWER(C2))),"Production",
-IF(ISNUMBER(SEARCH("fragrance",LOWER(C2))),"Production",
-IF(ISNUMBER(SEARCH("gohil",LOWER(C2))),"Production",
-IF(ISNUMBER(SEARCH("formulator",LOWER(C2))),"Production",
-IF(ISNUMBER(SEARCH("shea",LOWER(C2))),"Production",
-IF(ISNUMBER(SEARCH("olive",LOWER(C2))),"Production",
-IF(ISNUMBER(SEARCH("pack",LOWER(C2))),"Production",
-IF(ISNUMBER(SEARCH("sticker",LOWER(C2))),"Production",
-IF(ISNUMBER(SEARCH("ulinzi",LOWER(C2))),"Operating",
-IF(ISNUMBER(SEARCH("taka",LOWER(C2))),"Operating",
-IF(C2="TRA","Taxes",
-IF(C2="AUWSA","Operating",
-"Misc")))))))))))))))))))</f>
+        <f>IF(OR(ISNUMBER(SEARCH("mafuta",LOWER(C2))),ISNUMBER(SEARCH("soap",LOWER(C2))),ISNUMBER(SEARCH("oil",LOWER(C2))),ISNUMBER(SEARCH("fragrance",LOWER(C2))),ISNUMBER(SEARCH("caustic",LOWER(C2))),ISNUMBER(SEARCH("formulator",LOWER(C2))),ISNUMBER(SEARCH("viungo",LOWER(C2)))),"Production",
+IF(OR(ISNUMBER(SEARCH("abel",LOWER(C2))),ISNUMBER(SEARCH("boda",LOWER(C2))),ISNUMBER(SEARCH("mzigo",LOWER(C2))),ISNUMBER(SEARCH("nauli",LOWER(C2))),ISNUMBER(SEARCH("transport",LOWER(C2))),ISNUMBER(SEARCH("tumetuma",LOWER(C2)))),"Logistics",
+IF(OR(ISNUMBER(SEARCH("luku",LOWER(C2))),ISNUMBER(SEARCH("umeme",LOWER(C2))),ISNUMBER(SEARCH("maji",LOWER(C2))),ISNUMBER(SEARCH("auwsa",LOWER(C2))),ISNUMBER(SEARCH("ulinzi",LOWER(C2))),ISNUMBER(SEARCH("taka",LOWER(C2))),ISNUMBER(SEARCH("fundi",LOWER(C2))),ISNUMBER(SEARCH("rent",LOWER(C2)))),"Operating",
+IF(OR(ISNUMBER(SEARCH("mary",LOWER(C2))),ISNUMBER(SEARCH("marry",LOWER(C2)))),"Salaries",
+IF(OR(ISNUMBER(SEARCH("tra",LOWER(C2))),ISNUMBER(SEARCH("tax",LOWER(C2))),ISNUMBER(SEARCH("control",LOWER(C2)))),"Taxes",
+"Misc")))))</f>
         <v>Operating</v>
       </c>
       <c r="E2" s="13">
@@ -35564,8 +35610,8 @@
         <v>86</v>
       </c>
       <c r="H2" s="13">
-        <f>SUM(E2:E41)</f>
-        <v>548300</v>
+        <f>SUM(E2:E42)</f>
+        <v>1118300</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -35573,33 +35619,19 @@
         <v>46029</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B66" si="0">TEXT(A3, "mmm")</f>
+        <f t="shared" ref="B3:B67" si="0">TEXT(A3, "mmm")</f>
         <v>Jan</v>
       </c>
       <c r="C3" t="s">
         <v>101</v>
       </c>
       <c r="D3" t="str">
-        <f t="shared" ref="D3:D66" si="1">IF(ISNUMBER(SEARCH("nauli",LOWER(C3))),"Logistics",
-IF(ISNUMBER(SEARCH("lunch",LOWER(C3))),"Misc",
-IF(OR(ISNUMBER(SEARCH("luku",LOWER(C3))),ISNUMBER(SEARCH("umeme",LOWER(C3)))),"Operating",
-IF(ISNUMBER(SEARCH("boda",LOWER(C3))),"Logistics",
-IF(ISNUMBER(SEARCH("abel",LOWER(C3))),"Logistics",
-IF(ISNUMBER(SEARCH("toyo",LOWER(C3))),"Logistics",
-IF(ISNUMBER(SEARCH("mary",LOWER(C3))),"Salaries",
-IF(ISNUMBER(SEARCH("soap",LOWER(C3))),"Production",
-IF(ISNUMBER(SEARCH("fragrance",LOWER(C3))),"Production",
-IF(ISNUMBER(SEARCH("gohil",LOWER(C3))),"Production",
-IF(ISNUMBER(SEARCH("formulator",LOWER(C3))),"Production",
-IF(ISNUMBER(SEARCH("shea",LOWER(C3))),"Production",
-IF(ISNUMBER(SEARCH("olive",LOWER(C3))),"Production",
-IF(ISNUMBER(SEARCH("pack",LOWER(C3))),"Production",
-IF(ISNUMBER(SEARCH("sticker",LOWER(C3))),"Production",
-IF(ISNUMBER(SEARCH("ulinzi",LOWER(C3))),"Operating",
-IF(ISNUMBER(SEARCH("taka",LOWER(C3))),"Operating",
-IF(C3="TRA","Taxes",
-IF(C3="AUWSA","Operating",
-"Misc")))))))))))))))))))</f>
+        <f t="shared" ref="D3:D66" si="1">IF(OR(ISNUMBER(SEARCH("mafuta",LOWER(C3))),ISNUMBER(SEARCH("soap",LOWER(C3))),ISNUMBER(SEARCH("oil",LOWER(C3))),ISNUMBER(SEARCH("fragrance",LOWER(C3))),ISNUMBER(SEARCH("caustic",LOWER(C3))),ISNUMBER(SEARCH("formulator",LOWER(C3))),ISNUMBER(SEARCH("viungo",LOWER(C3)))),"Production",
+IF(OR(ISNUMBER(SEARCH("abel",LOWER(C3))),ISNUMBER(SEARCH("boda",LOWER(C3))),ISNUMBER(SEARCH("mzigo",LOWER(C3))),ISNUMBER(SEARCH("nauli",LOWER(C3))),ISNUMBER(SEARCH("transport",LOWER(C3))),ISNUMBER(SEARCH("tumetuma",LOWER(C3)))),"Logistics",
+IF(OR(ISNUMBER(SEARCH("luku",LOWER(C3))),ISNUMBER(SEARCH("umeme",LOWER(C3))),ISNUMBER(SEARCH("maji",LOWER(C3))),ISNUMBER(SEARCH("auwsa",LOWER(C3))),ISNUMBER(SEARCH("ulinzi",LOWER(C3))),ISNUMBER(SEARCH("taka",LOWER(C3))),ISNUMBER(SEARCH("fundi",LOWER(C3))),ISNUMBER(SEARCH("rent",LOWER(C3)))),"Operating",
+IF(OR(ISNUMBER(SEARCH("mary",LOWER(C3))),ISNUMBER(SEARCH("marry",LOWER(C3)))),"Salaries",
+IF(OR(ISNUMBER(SEARCH("tra",LOWER(C3))),ISNUMBER(SEARCH("tax",LOWER(C3))),ISNUMBER(SEARCH("control",LOWER(C3)))),"Taxes",
+"Misc")))))</f>
         <v>Logistics</v>
       </c>
       <c r="E3" s="13">
@@ -35609,8 +35641,8 @@
         <v>87</v>
       </c>
       <c r="H3" s="13">
-        <f>SUM(E42:E89)</f>
-        <v>833000</v>
+        <f>SUM(E43:E91)</f>
+        <v>1403000</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -35626,13 +35658,17 @@
       </c>
       <c r="D4" t="str">
         <f t="shared" si="1"/>
-        <v>Production</v>
+        <v>Misc</v>
       </c>
       <c r="E4" s="13">
         <v>40000</v>
       </c>
       <c r="G4" t="s">
         <v>94</v>
+      </c>
+      <c r="H4" s="13">
+        <f>SUM(E92:E146)</f>
+        <v>1754500</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -35648,10 +35684,17 @@
       </c>
       <c r="D5" t="str">
         <f t="shared" si="1"/>
-        <v>Production</v>
+        <v>Misc</v>
       </c>
       <c r="E5" s="13">
         <v>40000</v>
+      </c>
+      <c r="G5" t="s">
+        <v>187</v>
+      </c>
+      <c r="H5" s="13">
+        <f>SUM(H2:H4)</f>
+        <v>4275800</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -35819,7 +35862,7 @@
       </c>
       <c r="D14" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Production</v>
       </c>
       <c r="E14" s="13">
         <v>6000</v>
@@ -35895,7 +35938,7 @@
       </c>
       <c r="D18" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Production</v>
       </c>
       <c r="E18" s="13">
         <v>12000</v>
@@ -35933,7 +35976,7 @@
       </c>
       <c r="D20" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Operating</v>
       </c>
       <c r="E20" s="13">
         <v>6000</v>
@@ -35952,7 +35995,7 @@
       </c>
       <c r="D21" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E21" s="13">
         <v>21800</v>
@@ -36009,7 +36052,7 @@
       </c>
       <c r="D24" t="str">
         <f t="shared" si="1"/>
-        <v>Production</v>
+        <v>Misc</v>
       </c>
       <c r="E24" s="13">
         <v>25000</v>
@@ -36256,7 +36299,7 @@
       </c>
       <c r="D37" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Taxes</v>
       </c>
       <c r="E37" s="13">
         <v>6000</v>
@@ -36309,14 +36352,14 @@
         <v>Jan</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D40" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Operating</v>
       </c>
       <c r="E40" s="13">
-        <v>10000</v>
+        <v>570000</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -36328,52 +36371,52 @@
         <v>Jan</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D41" t="str">
         <f t="shared" si="1"/>
-        <v>Logistics</v>
+        <v>Operating</v>
       </c>
       <c r="E41" s="13">
-        <v>7000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>46055</v>
+        <v>46052</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="0"/>
-        <v>Feb</v>
+        <v>Jan</v>
       </c>
       <c r="C42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D42" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E42" s="13">
-        <v>6000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>46057</v>
+        <v>46055</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C43" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D43" t="str">
         <f t="shared" si="1"/>
         <v>Misc</v>
       </c>
       <c r="E43" s="13">
-        <v>2000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -36385,14 +36428,14 @@
         <v>Feb</v>
       </c>
       <c r="C44" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D44" t="str">
         <f t="shared" si="1"/>
-        <v>Production</v>
+        <v>Logistics</v>
       </c>
       <c r="E44" s="13">
-        <v>10000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -36404,33 +36447,33 @@
         <v>Feb</v>
       </c>
       <c r="C45" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D45" t="str">
         <f t="shared" si="1"/>
-        <v>Logistics</v>
+        <v>Misc</v>
       </c>
       <c r="E45" s="13">
-        <v>7000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C46" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D46" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E46" s="13">
-        <v>10000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -36442,14 +36485,14 @@
         <v>Feb</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D47" t="str">
         <f t="shared" si="1"/>
         <v>Misc</v>
       </c>
       <c r="E47" s="13">
-        <v>20000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -36461,52 +36504,52 @@
         <v>Feb</v>
       </c>
       <c r="C48" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="D48" t="str">
         <f t="shared" si="1"/>
         <v>Misc</v>
       </c>
       <c r="E48" s="13">
-        <v>2000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C49" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="D49" t="str">
         <f t="shared" si="1"/>
-        <v>Operating</v>
+        <v>Misc</v>
       </c>
       <c r="E49" s="13">
-        <v>20000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D50" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Operating</v>
       </c>
       <c r="E50" s="13">
-        <v>12000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -36518,14 +36561,14 @@
         <v>Feb</v>
       </c>
       <c r="C51" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D51" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Production</v>
       </c>
       <c r="E51" s="13">
-        <v>2000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -36537,33 +36580,33 @@
         <v>Feb</v>
       </c>
       <c r="C52" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D52" t="str">
         <f t="shared" si="1"/>
         <v>Misc</v>
       </c>
       <c r="E52" s="13">
-        <v>70000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C53" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D53" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Salaries</v>
       </c>
       <c r="E53" s="13">
-        <v>2000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -36575,14 +36618,14 @@
         <v>Feb</v>
       </c>
       <c r="C54" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D54" t="str">
         <f t="shared" si="1"/>
         <v>Misc</v>
       </c>
       <c r="E54" s="13">
-        <v>10000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -36594,14 +36637,14 @@
         <v>Feb</v>
       </c>
       <c r="C55" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D55" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Operating</v>
       </c>
       <c r="E55" s="13">
-        <v>50000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -36613,52 +36656,52 @@
         <v>Feb</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="D56" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Salaries</v>
       </c>
       <c r="E56" s="13">
-        <v>7500</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C57" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="D57" t="str">
         <f t="shared" si="1"/>
-        <v>Logistics</v>
+        <v>Misc</v>
       </c>
       <c r="E57" s="13">
-        <v>1000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C58" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D58" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E58" s="13">
-        <v>33000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -36670,14 +36713,14 @@
         <v>Feb</v>
       </c>
       <c r="C59" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D59" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Production</v>
       </c>
       <c r="E59" s="13">
-        <v>10000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -36689,52 +36732,52 @@
         <v>Feb</v>
       </c>
       <c r="C60" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="D60" t="str">
         <f t="shared" si="1"/>
-        <v>Production</v>
+        <v>Misc</v>
       </c>
       <c r="E60" s="13">
-        <v>30000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C61" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="D61" t="str">
         <f t="shared" si="1"/>
-        <v>Logistics</v>
+        <v>Misc</v>
       </c>
       <c r="E61" s="13">
-        <v>10000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C62" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="D62" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E62" s="13">
-        <v>7500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -36746,14 +36789,14 @@
         <v>Feb</v>
       </c>
       <c r="C63" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="D63" t="str">
         <f t="shared" si="1"/>
-        <v>Production</v>
+        <v>Misc</v>
       </c>
       <c r="E63" s="13">
-        <v>45000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -36765,52 +36808,52 @@
         <v>Feb</v>
       </c>
       <c r="C64" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="D64" t="str">
         <f t="shared" si="1"/>
-        <v>Logistics</v>
+        <v>Misc</v>
       </c>
       <c r="E64" s="13">
-        <v>12000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C65" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="D65" t="str">
         <f t="shared" si="1"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E65" s="13">
-        <v>3000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C66" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D66" t="str">
         <f t="shared" si="1"/>
         <v>Misc</v>
       </c>
       <c r="E66" s="13">
-        <v>6000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -36818,37 +36861,23 @@
         <v>46071</v>
       </c>
       <c r="B67" t="str">
-        <f t="shared" ref="B67:B110" si="2">TEXT(A67, "mmm")</f>
+        <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="D67" t="str">
-        <f t="shared" ref="D67:D108" si="3">IF(ISNUMBER(SEARCH("nauli",LOWER(C67))),"Logistics",
-IF(ISNUMBER(SEARCH("lunch",LOWER(C67))),"Misc",
-IF(OR(ISNUMBER(SEARCH("luku",LOWER(C67))),ISNUMBER(SEARCH("umeme",LOWER(C67)))),"Operating",
-IF(ISNUMBER(SEARCH("boda",LOWER(C67))),"Logistics",
-IF(ISNUMBER(SEARCH("abel",LOWER(C67))),"Logistics",
-IF(ISNUMBER(SEARCH("toyo",LOWER(C67))),"Logistics",
-IF(ISNUMBER(SEARCH("mary",LOWER(C67))),"Salaries",
-IF(ISNUMBER(SEARCH("soap",LOWER(C67))),"Production",
-IF(ISNUMBER(SEARCH("fragrance",LOWER(C67))),"Production",
-IF(ISNUMBER(SEARCH("gohil",LOWER(C67))),"Production",
-IF(ISNUMBER(SEARCH("formulator",LOWER(C67))),"Production",
-IF(ISNUMBER(SEARCH("shea",LOWER(C67))),"Production",
-IF(ISNUMBER(SEARCH("olive",LOWER(C67))),"Production",
-IF(ISNUMBER(SEARCH("pack",LOWER(C67))),"Production",
-IF(ISNUMBER(SEARCH("sticker",LOWER(C67))),"Production",
-IF(ISNUMBER(SEARCH("ulinzi",LOWER(C67))),"Operating",
-IF(ISNUMBER(SEARCH("taka",LOWER(C67))),"Operating",
-IF(C67="TRA","Taxes",
-IF(C67="AUWSA","Operating",
-"Misc")))))))))))))))))))</f>
-        <v>Logistics</v>
+        <f t="shared" ref="D67:D131" si="2">IF(OR(ISNUMBER(SEARCH("mafuta",LOWER(C67))),ISNUMBER(SEARCH("soap",LOWER(C67))),ISNUMBER(SEARCH("oil",LOWER(C67))),ISNUMBER(SEARCH("fragrance",LOWER(C67))),ISNUMBER(SEARCH("caustic",LOWER(C67))),ISNUMBER(SEARCH("formulator",LOWER(C67))),ISNUMBER(SEARCH("viungo",LOWER(C67)))),"Production",
+IF(OR(ISNUMBER(SEARCH("abel",LOWER(C67))),ISNUMBER(SEARCH("boda",LOWER(C67))),ISNUMBER(SEARCH("mzigo",LOWER(C67))),ISNUMBER(SEARCH("nauli",LOWER(C67))),ISNUMBER(SEARCH("transport",LOWER(C67))),ISNUMBER(SEARCH("tumetuma",LOWER(C67)))),"Logistics",
+IF(OR(ISNUMBER(SEARCH("luku",LOWER(C67))),ISNUMBER(SEARCH("umeme",LOWER(C67))),ISNUMBER(SEARCH("maji",LOWER(C67))),ISNUMBER(SEARCH("auwsa",LOWER(C67))),ISNUMBER(SEARCH("ulinzi",LOWER(C67))),ISNUMBER(SEARCH("taka",LOWER(C67))),ISNUMBER(SEARCH("fundi",LOWER(C67))),ISNUMBER(SEARCH("rent",LOWER(C67)))),"Operating",
+IF(OR(ISNUMBER(SEARCH("mary",LOWER(C67))),ISNUMBER(SEARCH("marry",LOWER(C67)))),"Salaries",
+IF(OR(ISNUMBER(SEARCH("tra",LOWER(C67))),ISNUMBER(SEARCH("tax",LOWER(C67))),ISNUMBER(SEARCH("control",LOWER(C67)))),"Taxes",
+"Misc")))))</f>
+        <v>Misc</v>
       </c>
       <c r="E67" s="13">
-        <v>7000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -36856,18 +36885,18 @@
         <v>46071</v>
       </c>
       <c r="B68" t="str">
+        <f t="shared" ref="B68:B142" si="3">TEXT(A68, "mmm")</f>
+        <v>Feb</v>
+      </c>
+      <c r="C68" t="s">
+        <v>148</v>
+      </c>
+      <c r="D68" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C68" t="s">
-        <v>150</v>
-      </c>
-      <c r="D68" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E68" s="13">
-        <v>6000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -36875,18 +36904,18 @@
         <v>46071</v>
       </c>
       <c r="B69" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C69" t="s">
+        <v>150</v>
+      </c>
+      <c r="D69" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C69" t="s">
-        <v>141</v>
-      </c>
-      <c r="D69" t="str">
-        <f t="shared" si="3"/>
         <v>Misc</v>
       </c>
       <c r="E69" s="13">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -36894,18 +36923,18 @@
         <v>46071</v>
       </c>
       <c r="B70" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C70" t="s">
+        <v>141</v>
+      </c>
+      <c r="D70" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C70" t="s">
-        <v>124</v>
-      </c>
-      <c r="D70" t="str">
-        <f t="shared" si="3"/>
-        <v>Logistics</v>
+        <v>Misc</v>
       </c>
       <c r="E70" s="13">
-        <v>16000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -36913,37 +36942,37 @@
         <v>46071</v>
       </c>
       <c r="B71" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C71" t="s">
+        <v>124</v>
+      </c>
+      <c r="D71" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C71" t="s">
-        <v>151</v>
-      </c>
-      <c r="D71" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E71" s="13">
-        <v>4000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>46076</v>
+        <v>46071</v>
       </c>
       <c r="B72" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C72" t="s">
+        <v>151</v>
+      </c>
+      <c r="D72" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C72" t="s">
-        <v>152</v>
-      </c>
-      <c r="D72" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Operating</v>
       </c>
       <c r="E72" s="13">
-        <v>10000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -36951,18 +36980,18 @@
         <v>46076</v>
       </c>
       <c r="B73" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C73" t="s">
+        <v>152</v>
+      </c>
+      <c r="D73" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C73" t="s">
-        <v>145</v>
-      </c>
-      <c r="D73" t="str">
-        <f t="shared" si="3"/>
-        <v>Logistics</v>
+        <v>Misc</v>
       </c>
       <c r="E73" s="13">
-        <v>6000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -36970,18 +36999,18 @@
         <v>46076</v>
       </c>
       <c r="B74" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C74" t="s">
+        <v>145</v>
+      </c>
+      <c r="D74" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C74" t="s">
-        <v>142</v>
-      </c>
-      <c r="D74" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E74" s="13">
-        <v>20000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -36989,75 +37018,75 @@
         <v>46076</v>
       </c>
       <c r="B75" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C75" t="s">
+        <v>142</v>
+      </c>
+      <c r="D75" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C75" t="s">
-        <v>147</v>
-      </c>
-      <c r="D75" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Salaries</v>
       </c>
       <c r="E75" s="13">
-        <v>10000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="B76" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C76" t="s">
+        <v>147</v>
+      </c>
+      <c r="D76" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C76" t="s">
-        <v>107</v>
-      </c>
-      <c r="D76" t="str">
-        <f t="shared" si="3"/>
         <v>Misc</v>
       </c>
       <c r="E76" s="13">
-        <v>6000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="B77" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C77" t="s">
+        <v>107</v>
+      </c>
+      <c r="D77" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C77" t="s">
-        <v>124</v>
-      </c>
-      <c r="D77" t="str">
-        <f t="shared" si="3"/>
-        <v>Logistics</v>
+        <v>Misc</v>
       </c>
       <c r="E77" s="13">
-        <v>17000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="B78" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C78" t="s">
+        <v>124</v>
+      </c>
+      <c r="D78" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C78" t="s">
-        <v>153</v>
-      </c>
-      <c r="D78" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E78" s="13">
-        <v>20000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -37065,18 +37094,18 @@
         <v>46079</v>
       </c>
       <c r="B79" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C79" t="s">
+        <v>153</v>
+      </c>
+      <c r="D79" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C79" t="s">
-        <v>154</v>
-      </c>
-      <c r="D79" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Taxes</v>
       </c>
       <c r="E79" s="13">
-        <v>10000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -37084,18 +37113,18 @@
         <v>46079</v>
       </c>
       <c r="B80" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C80" t="s">
+        <v>154</v>
+      </c>
+      <c r="D80" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C80" t="s">
-        <v>155</v>
-      </c>
-      <c r="D80" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Operating</v>
       </c>
       <c r="E80" s="13">
-        <v>65000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -37103,18 +37132,18 @@
         <v>46079</v>
       </c>
       <c r="B81" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C81" t="s">
+        <v>155</v>
+      </c>
+      <c r="D81" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C81" t="s">
-        <v>130</v>
-      </c>
-      <c r="D81" t="str">
-        <f t="shared" si="3"/>
-        <v>Operating</v>
+        <v>Logistics</v>
       </c>
       <c r="E81" s="13">
-        <v>10000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -37122,18 +37151,18 @@
         <v>46079</v>
       </c>
       <c r="B82" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C82" t="s">
+        <v>130</v>
+      </c>
+      <c r="D82" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C82" t="s">
-        <v>129</v>
-      </c>
-      <c r="D82" t="str">
-        <f t="shared" si="3"/>
         <v>Operating</v>
       </c>
       <c r="E82" s="13">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -37141,37 +37170,37 @@
         <v>46079</v>
       </c>
       <c r="B83" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C83" t="s">
+        <v>129</v>
+      </c>
+      <c r="D83" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C83" t="s">
-        <v>107</v>
-      </c>
-      <c r="D83" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Operating</v>
       </c>
       <c r="E83" s="13">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="B84" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C84" t="s">
+        <v>107</v>
+      </c>
+      <c r="D84" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C84" t="s">
-        <v>145</v>
-      </c>
-      <c r="D84" t="str">
-        <f t="shared" si="3"/>
-        <v>Logistics</v>
+        <v>Misc</v>
       </c>
       <c r="E84" s="13">
-        <v>6000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -37179,18 +37208,18 @@
         <v>46080</v>
       </c>
       <c r="B85" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C85" t="s">
+        <v>145</v>
+      </c>
+      <c r="D85" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C85" t="s">
-        <v>156</v>
-      </c>
-      <c r="D85" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E85" s="13">
-        <v>2000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -37198,18 +37227,18 @@
         <v>46080</v>
       </c>
       <c r="B86" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C86" t="s">
+        <v>156</v>
+      </c>
+      <c r="D86" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C86" t="s">
-        <v>124</v>
-      </c>
-      <c r="D86" t="str">
-        <f t="shared" si="3"/>
-        <v>Logistics</v>
+        <v>Misc</v>
       </c>
       <c r="E86" s="13">
-        <v>11000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -37217,18 +37246,18 @@
         <v>46080</v>
       </c>
       <c r="B87" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C87" t="s">
+        <v>124</v>
+      </c>
+      <c r="D87" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C87" t="s">
-        <v>157</v>
-      </c>
-      <c r="D87" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E87" s="13">
-        <v>150000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -37236,113 +37265,113 @@
         <v>46080</v>
       </c>
       <c r="B88" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C88" t="s">
+        <v>157</v>
+      </c>
+      <c r="D88" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C88" t="s">
-        <v>158</v>
-      </c>
-      <c r="D88" t="str">
-        <f t="shared" si="3"/>
         <v>Misc</v>
       </c>
       <c r="E88" s="13">
-        <v>50000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="B89" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C89" t="s">
+        <v>158</v>
+      </c>
+      <c r="D89" t="str">
         <f t="shared" si="2"/>
-        <v>Feb</v>
-      </c>
-      <c r="C89" t="s">
-        <v>159</v>
-      </c>
-      <c r="D89" t="str">
-        <f t="shared" si="3"/>
         <v>Misc</v>
       </c>
       <c r="E89" s="13">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="B90" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C90" t="s">
+        <v>188</v>
+      </c>
+      <c r="D90" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C90" t="s">
-        <v>107</v>
-      </c>
-      <c r="D90" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Operating</v>
       </c>
       <c r="E90" s="13">
-        <v>8000</v>
+        <v>570000</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>46085</v>
+        <v>46081</v>
       </c>
       <c r="B91" t="str">
+        <f t="shared" si="3"/>
+        <v>Feb</v>
+      </c>
+      <c r="C91" t="s">
+        <v>159</v>
+      </c>
+      <c r="D91" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C91" t="s">
-        <v>142</v>
-      </c>
-      <c r="D91" t="str">
-        <f t="shared" si="3"/>
         <v>Misc</v>
       </c>
       <c r="E91" s="13">
-        <v>50000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>46087</v>
+        <v>46085</v>
       </c>
       <c r="B92" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C92" t="s">
+        <v>107</v>
+      </c>
+      <c r="D92" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C92" t="s">
-        <v>160</v>
-      </c>
-      <c r="D92" t="str">
-        <f t="shared" si="3"/>
         <v>Misc</v>
       </c>
       <c r="E92" s="13">
-        <v>3000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>46087</v>
+        <v>46085</v>
       </c>
       <c r="B93" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C93" t="s">
+        <v>142</v>
+      </c>
+      <c r="D93" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C93" t="s">
-        <v>109</v>
-      </c>
-      <c r="D93" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Salaries</v>
       </c>
       <c r="E93" s="13">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -37350,18 +37379,18 @@
         <v>46087</v>
       </c>
       <c r="B94" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C94" t="s">
+        <v>160</v>
+      </c>
+      <c r="D94" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C94" t="s">
-        <v>161</v>
-      </c>
-      <c r="D94" t="str">
-        <f t="shared" si="3"/>
-        <v>Production</v>
+        <v>Misc</v>
       </c>
       <c r="E94" s="13">
-        <v>55000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -37369,14 +37398,14 @@
         <v>46087</v>
       </c>
       <c r="B95" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C95" t="s">
+        <v>109</v>
+      </c>
+      <c r="D95" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C95" t="s">
-        <v>162</v>
-      </c>
-      <c r="D95" t="str">
-        <f t="shared" si="3"/>
         <v>Misc</v>
       </c>
       <c r="E95" s="13">
@@ -37385,36 +37414,36 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>46090</v>
+        <v>46087</v>
       </c>
       <c r="B96" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C96" t="s">
+        <v>161</v>
+      </c>
+      <c r="D96" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C96" t="s">
-        <v>148</v>
-      </c>
-      <c r="D96" t="str">
-        <f t="shared" si="3"/>
-        <v>Logistics</v>
+        <v>Production</v>
       </c>
       <c r="E96" s="13">
-        <v>10000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>46090</v>
+        <v>46087</v>
       </c>
       <c r="B97" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C97" t="s">
+        <v>162</v>
+      </c>
+      <c r="D97" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C97" t="s">
-        <v>163</v>
-      </c>
-      <c r="D97" t="str">
-        <f t="shared" si="3"/>
         <v>Misc</v>
       </c>
       <c r="E97" s="13">
@@ -37423,40 +37452,40 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="B98" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C98" t="s">
+        <v>148</v>
+      </c>
+      <c r="D98" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C98" t="s">
-        <v>142</v>
-      </c>
-      <c r="D98" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Logistics</v>
       </c>
       <c r="E98" s="13">
-        <v>100000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="B99" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C99" t="s">
+        <v>163</v>
+      </c>
+      <c r="D99" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C99" t="s">
-        <v>164</v>
-      </c>
-      <c r="D99" t="str">
-        <f t="shared" si="3"/>
         <v>Misc</v>
       </c>
       <c r="E99" s="13">
-        <v>20000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -37464,72 +37493,72 @@
         <v>46088</v>
       </c>
       <c r="B100" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C100" t="s">
+        <v>142</v>
+      </c>
+      <c r="D100" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C100" t="s">
-        <v>127</v>
-      </c>
-      <c r="D100" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Salaries</v>
       </c>
       <c r="E100" s="13">
-        <v>6000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>46091</v>
+        <v>46088</v>
       </c>
       <c r="B101" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C101" t="s">
+        <v>164</v>
+      </c>
+      <c r="D101" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C101" t="s">
-        <v>165</v>
-      </c>
-      <c r="D101" t="str">
-        <f t="shared" si="3"/>
         <v>Misc</v>
       </c>
       <c r="E101" s="13">
-        <v>5000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>46091</v>
+        <v>46088</v>
       </c>
       <c r="B102" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C102" t="s">
+        <v>127</v>
+      </c>
+      <c r="D102" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C102" t="s">
-        <v>166</v>
-      </c>
-      <c r="D102" t="str">
-        <f t="shared" si="3"/>
         <v>Misc</v>
       </c>
       <c r="E102" s="13">
-        <v>50000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="B103" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C103" t="s">
+        <v>165</v>
+      </c>
+      <c r="D103" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C103" t="s">
-        <v>107</v>
-      </c>
-      <c r="D103" t="str">
-        <f t="shared" si="3"/>
-        <v>Misc</v>
+        <v>Operating</v>
       </c>
       <c r="E103" s="13">
         <v>5000</v>
@@ -37537,21 +37566,21 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="B104" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C104" t="s">
+        <v>166</v>
+      </c>
+      <c r="D104" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C104" t="s">
-        <v>167</v>
-      </c>
-      <c r="D104" t="str">
-        <f t="shared" si="3"/>
-        <v>Taxes</v>
+        <v>Production</v>
       </c>
       <c r="E104" s="13">
-        <v>25000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -37559,18 +37588,18 @@
         <v>46092</v>
       </c>
       <c r="B105" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Mar</v>
       </c>
       <c r="C105" t="s">
         <v>107</v>
       </c>
       <c r="D105" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>Misc</v>
       </c>
       <c r="E105" s="13">
-        <v>6000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -37578,18 +37607,18 @@
         <v>46092</v>
       </c>
       <c r="B106" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C106" t="s">
+        <v>167</v>
+      </c>
+      <c r="D106" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C106" t="s">
-        <v>120</v>
-      </c>
-      <c r="D106" t="str">
-        <f t="shared" si="3"/>
-        <v>Production</v>
+        <v>Taxes</v>
       </c>
       <c r="E106" s="13">
-        <v>60000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -37597,55 +37626,764 @@
         <v>46092</v>
       </c>
       <c r="B107" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C107" t="s">
+        <v>107</v>
+      </c>
+      <c r="D107" t="str">
         <f t="shared" si="2"/>
-        <v>Mar</v>
-      </c>
-      <c r="C107" t="s">
-        <v>168</v>
-      </c>
-      <c r="D107" t="str">
-        <f t="shared" si="3"/>
-        <v>Operating</v>
+        <v>Misc</v>
       </c>
       <c r="E107" s="13">
-        <v>35000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B108" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C108" t="s">
+        <v>120</v>
+      </c>
+      <c r="D108" t="str">
+        <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E108" s="13">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B109" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C109" t="s">
+        <v>168</v>
+      </c>
+      <c r="D109" t="str">
+        <f t="shared" si="2"/>
+        <v>Operating</v>
+      </c>
+      <c r="E109" s="13">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="3">
         <v>46097</v>
       </c>
-      <c r="B108" t="str">
+      <c r="B110" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C110" t="s">
+        <v>121</v>
+      </c>
+      <c r="D110" t="str">
         <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E110" s="13">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="23">
+        <v>46097</v>
+      </c>
+      <c r="B111" t="str">
+        <f t="shared" si="3"/>
         <v>Mar</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C111" t="s">
+        <v>173</v>
+      </c>
+      <c r="D111" t="str">
+        <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E111" s="13">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="23">
+        <v>46097</v>
+      </c>
+      <c r="B112" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C112" t="s">
+        <v>169</v>
+      </c>
+      <c r="D112" t="str">
+        <f t="shared" si="2"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E112" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="23">
+        <v>46098</v>
+      </c>
+      <c r="B113" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C113" t="s">
         <v>121</v>
       </c>
-      <c r="D108" t="str">
+      <c r="D113" t="str">
+        <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E113" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="23">
+        <v>46098</v>
+      </c>
+      <c r="B114" t="str">
         <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C114" t="s">
+        <v>170</v>
+      </c>
+      <c r="D114" t="str">
+        <f t="shared" si="2"/>
         <v>Misc</v>
       </c>
-      <c r="E108" s="13">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="23">
-        <v>46097</v>
-      </c>
-      <c r="B109" t="str">
+      <c r="E114" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="23">
+        <v>46098</v>
+      </c>
+      <c r="B115" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C115" t="s">
+        <v>147</v>
+      </c>
+      <c r="D115" t="str">
         <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E115" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="23">
+        <v>46098</v>
+      </c>
+      <c r="B116" t="str">
+        <f t="shared" si="3"/>
         <v>Mar</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="23">
-        <v>46097</v>
-      </c>
-      <c r="B110" t="str">
+      <c r="C116" t="s">
+        <v>171</v>
+      </c>
+      <c r="D116" t="str">
         <f t="shared" si="2"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E116" s="13">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="23">
+        <v>46098</v>
+      </c>
+      <c r="B117" t="str">
+        <f t="shared" si="3"/>
         <v>Mar</v>
+      </c>
+      <c r="C117" t="s">
+        <v>172</v>
+      </c>
+      <c r="D117" t="str">
+        <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E117" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="23">
+        <v>46099</v>
+      </c>
+      <c r="B118" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C118" t="s">
+        <v>166</v>
+      </c>
+      <c r="D118" t="str">
+        <f t="shared" si="2"/>
+        <v>Production</v>
+      </c>
+      <c r="E118" s="13">
+        <v>66500</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="23">
+        <v>46100</v>
+      </c>
+      <c r="B119" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C119" t="s">
+        <v>174</v>
+      </c>
+      <c r="D119" t="str">
+        <f t="shared" si="2"/>
+        <v>Production</v>
+      </c>
+      <c r="E119" s="13">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="23">
+        <v>46100</v>
+      </c>
+      <c r="B120" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C120" t="s">
+        <v>141</v>
+      </c>
+      <c r="D120" t="str">
+        <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E120" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="23">
+        <v>46100</v>
+      </c>
+      <c r="B121" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C121" t="s">
+        <v>175</v>
+      </c>
+      <c r="D121" t="str">
+        <f t="shared" si="2"/>
+        <v>Production</v>
+      </c>
+      <c r="E121" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="23">
+        <v>46101</v>
+      </c>
+      <c r="B122" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C122" t="s">
+        <v>176</v>
+      </c>
+      <c r="D122" t="str">
+        <f t="shared" si="2"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E122" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="23">
+        <v>46101</v>
+      </c>
+      <c r="B123" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C123" t="s">
+        <v>177</v>
+      </c>
+      <c r="D123" t="str">
+        <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E123" s="13">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="23">
+        <v>46104</v>
+      </c>
+      <c r="B124" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C124" t="s">
+        <v>132</v>
+      </c>
+      <c r="D124" t="str">
+        <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E124" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="23">
+        <v>46104</v>
+      </c>
+      <c r="B125" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C125" t="s">
+        <v>148</v>
+      </c>
+      <c r="D125" t="str">
+        <f t="shared" si="2"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E125" s="13">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="23">
+        <v>46104</v>
+      </c>
+      <c r="B126" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C126" t="s">
+        <v>107</v>
+      </c>
+      <c r="D126" t="str">
+        <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E126" s="13">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="23">
+        <v>46104</v>
+      </c>
+      <c r="B127" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C127" t="s">
+        <v>178</v>
+      </c>
+      <c r="D127" t="str">
+        <f t="shared" si="2"/>
+        <v>Operating</v>
+      </c>
+      <c r="E127" s="13">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="23">
+        <v>46106</v>
+      </c>
+      <c r="B128" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C128" t="s">
+        <v>179</v>
+      </c>
+      <c r="D128" t="str">
+        <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E128" s="13">
+        <v>91000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="23">
+        <v>46106</v>
+      </c>
+      <c r="B129" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C129" t="s">
+        <v>180</v>
+      </c>
+      <c r="D129" t="str">
+        <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E129" s="13">
+        <v>57500</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="23">
+        <v>46106</v>
+      </c>
+      <c r="B130" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C130" t="s">
+        <v>181</v>
+      </c>
+      <c r="D130" t="str">
+        <f t="shared" si="2"/>
+        <v>Misc</v>
+      </c>
+      <c r="E130" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="23">
+        <v>46106</v>
+      </c>
+      <c r="B131" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C131" t="s">
+        <v>182</v>
+      </c>
+      <c r="D131" t="str">
+        <f t="shared" si="2"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E131" s="13">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="23">
+        <v>46106</v>
+      </c>
+      <c r="B132" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C132" t="s">
+        <v>165</v>
+      </c>
+      <c r="D132" t="str">
+        <f t="shared" ref="D132:D146" si="4">IF(OR(ISNUMBER(SEARCH("mafuta",LOWER(C132))),ISNUMBER(SEARCH("soap",LOWER(C132))),ISNUMBER(SEARCH("oil",LOWER(C132))),ISNUMBER(SEARCH("fragrance",LOWER(C132))),ISNUMBER(SEARCH("caustic",LOWER(C132))),ISNUMBER(SEARCH("formulator",LOWER(C132))),ISNUMBER(SEARCH("viungo",LOWER(C132)))),"Production",
+IF(OR(ISNUMBER(SEARCH("abel",LOWER(C132))),ISNUMBER(SEARCH("boda",LOWER(C132))),ISNUMBER(SEARCH("mzigo",LOWER(C132))),ISNUMBER(SEARCH("nauli",LOWER(C132))),ISNUMBER(SEARCH("transport",LOWER(C132))),ISNUMBER(SEARCH("tumetuma",LOWER(C132)))),"Logistics",
+IF(OR(ISNUMBER(SEARCH("luku",LOWER(C132))),ISNUMBER(SEARCH("umeme",LOWER(C132))),ISNUMBER(SEARCH("maji",LOWER(C132))),ISNUMBER(SEARCH("auwsa",LOWER(C132))),ISNUMBER(SEARCH("ulinzi",LOWER(C132))),ISNUMBER(SEARCH("taka",LOWER(C132))),ISNUMBER(SEARCH("fundi",LOWER(C132))),ISNUMBER(SEARCH("rent",LOWER(C132)))),"Operating",
+IF(OR(ISNUMBER(SEARCH("mary",LOWER(C132))),ISNUMBER(SEARCH("marry",LOWER(C132)))),"Salaries",
+IF(OR(ISNUMBER(SEARCH("tra",LOWER(C132))),ISNUMBER(SEARCH("tax",LOWER(C132))),ISNUMBER(SEARCH("control",LOWER(C132)))),"Taxes",
+"Misc")))))</f>
+        <v>Operating</v>
+      </c>
+      <c r="E132" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="23">
+        <v>46106</v>
+      </c>
+      <c r="B133" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C133" t="s">
+        <v>176</v>
+      </c>
+      <c r="D133" t="str">
+        <f t="shared" si="4"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E133" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="23">
+        <v>46106</v>
+      </c>
+      <c r="B134" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C134" t="s">
+        <v>107</v>
+      </c>
+      <c r="D134" t="str">
+        <f t="shared" si="4"/>
+        <v>Misc</v>
+      </c>
+      <c r="E134" s="13">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="23">
+        <v>46106</v>
+      </c>
+      <c r="B135" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C135" t="s">
+        <v>183</v>
+      </c>
+      <c r="D135" t="str">
+        <f t="shared" si="4"/>
+        <v>Misc</v>
+      </c>
+      <c r="E135" s="13">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="23">
+        <v>46108</v>
+      </c>
+      <c r="B136" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C136" t="s">
+        <v>107</v>
+      </c>
+      <c r="D136" t="str">
+        <f t="shared" si="4"/>
+        <v>Misc</v>
+      </c>
+      <c r="E136" s="13">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="23">
+        <v>46109</v>
+      </c>
+      <c r="B137" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C137" t="s">
+        <v>145</v>
+      </c>
+      <c r="D137" t="str">
+        <f t="shared" si="4"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E137" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="23">
+        <v>46109</v>
+      </c>
+      <c r="B138" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C138" t="s">
+        <v>107</v>
+      </c>
+      <c r="D138" t="str">
+        <f t="shared" si="4"/>
+        <v>Misc</v>
+      </c>
+      <c r="E138" s="13">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="23">
+        <v>46109</v>
+      </c>
+      <c r="B139" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C139" t="s">
+        <v>184</v>
+      </c>
+      <c r="D139" t="str">
+        <f t="shared" si="4"/>
+        <v>Logistics</v>
+      </c>
+      <c r="E139" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="23">
+        <v>46111</v>
+      </c>
+      <c r="B140" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C140" t="s">
+        <v>129</v>
+      </c>
+      <c r="D140" t="str">
+        <f t="shared" si="4"/>
+        <v>Operating</v>
+      </c>
+      <c r="E140" s="13">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="23">
+        <v>46111</v>
+      </c>
+      <c r="B141" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C141" t="s">
+        <v>185</v>
+      </c>
+      <c r="D141" t="str">
+        <f t="shared" si="4"/>
+        <v>Misc</v>
+      </c>
+      <c r="E141" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" s="23">
+        <v>46112</v>
+      </c>
+      <c r="B142" t="str">
+        <f t="shared" si="3"/>
+        <v>Mar</v>
+      </c>
+      <c r="C142" t="s">
+        <v>130</v>
+      </c>
+      <c r="D142" t="str">
+        <f t="shared" si="4"/>
+        <v>Operating</v>
+      </c>
+      <c r="E142" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="23">
+        <v>46112</v>
+      </c>
+      <c r="B143" t="str">
+        <f t="shared" ref="B143:B146" si="5">TEXT(A143, "mmm")</f>
+        <v>Mar</v>
+      </c>
+      <c r="C143" t="s">
+        <v>161</v>
+      </c>
+      <c r="D143" t="str">
+        <f t="shared" si="4"/>
+        <v>Production</v>
+      </c>
+      <c r="E143" s="13">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="23">
+        <v>46112</v>
+      </c>
+      <c r="B144" t="str">
+        <f t="shared" si="5"/>
+        <v>Mar</v>
+      </c>
+      <c r="C144" t="s">
+        <v>186</v>
+      </c>
+      <c r="D144" t="str">
+        <f t="shared" si="4"/>
+        <v>Production</v>
+      </c>
+      <c r="E144" s="13">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" s="23">
+        <v>46112</v>
+      </c>
+      <c r="B145" t="str">
+        <f t="shared" si="5"/>
+        <v>Mar</v>
+      </c>
+      <c r="C145" t="s">
+        <v>167</v>
+      </c>
+      <c r="D145" t="str">
+        <f t="shared" si="4"/>
+        <v>Taxes</v>
+      </c>
+      <c r="E145" s="13">
+        <v>62500</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="23">
+        <v>46112</v>
+      </c>
+      <c r="B146" t="str">
+        <f t="shared" si="5"/>
+        <v>Mar</v>
+      </c>
+      <c r="C146" t="s">
+        <v>188</v>
+      </c>
+      <c r="D146" t="str">
+        <f t="shared" si="4"/>
+        <v>Operating</v>
+      </c>
+      <c r="E146" s="13">
+        <v>570000</v>
       </c>
     </row>
   </sheetData>
